--- a/database_sheets/all_products.xlsx
+++ b/database_sheets/all_products.xlsx
@@ -442,7 +442,7 @@
         <v>14.99</v>
       </c>
       <c r="G2">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
